--- a/2. Báo cáo - giấy tờ/1. Báo cáo/Báo cáo 2026/Bảo hành/TongHopXLBH_2609.xlsx
+++ b/2. Báo cáo - giấy tờ/1. Báo cáo/Báo cáo 2026/Bảo hành/TongHopXLBH_2609.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SXBH\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\1. Báo cáo\Báo cáo 2026\Bảo hành\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F350C41-3D51-4054-A607-442B94725D85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA8340D2-915E-4AF9-AAC3-E5B606BE175B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,26 +19,17 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$Q$270</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1631" uniqueCount="642">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1630" uniqueCount="642">
   <si>
     <t>H</t>
   </si>
@@ -2402,7 +2393,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2541,9 +2532,6 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2596,9 +2584,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3283,7 +3268,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="60" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" ht="45" x14ac:dyDescent="0.25">
       <c r="A12" s="15">
         <v>8</v>
       </c>
@@ -4066,7 +4051,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="15">
         <v>27</v>
       </c>
@@ -4912,7 +4897,7 @@
       <c r="P54" s="18"/>
       <c r="Q54" s="18"/>
     </row>
-    <row r="55" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="15">
         <v>51</v>
       </c>
@@ -5439,7 +5424,7 @@
       <c r="P71" s="18"/>
       <c r="Q71" s="18"/>
     </row>
-    <row r="72" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="15">
         <v>68</v>
       </c>
@@ -7886,7 +7871,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="139" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A139" s="15">
         <v>135</v>
       </c>
@@ -8602,7 +8587,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A161" s="15">
         <v>157</v>
       </c>
@@ -9754,7 +9739,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="191" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:17" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A191" s="15">
         <v>187</v>
       </c>
@@ -9834,7 +9819,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="193" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:17" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A193" s="15">
         <v>189</v>
       </c>
@@ -9871,7 +9856,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="194" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:17" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A194" s="15">
         <v>190</v>
       </c>
@@ -9910,7 +9895,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="195" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:17" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A195" s="15">
         <v>191</v>
       </c>
@@ -9953,7 +9938,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="196" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:17" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A196" s="15">
         <v>192</v>
       </c>
@@ -9992,7 +9977,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="197" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:17" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A197" s="15">
         <v>193</v>
       </c>
@@ -10033,7 +10018,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="198" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:17" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A198" s="15">
         <v>194</v>
       </c>
@@ -10074,7 +10059,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="199" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:17" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A199" s="15">
         <v>195</v>
       </c>
@@ -10152,7 +10137,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="201" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:17" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A201" s="15">
         <v>197</v>
       </c>
@@ -10193,7 +10178,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="202" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:17" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A202" s="15">
         <v>198</v>
       </c>
@@ -10275,7 +10260,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="204" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:17" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A204" s="15">
         <v>200</v>
       </c>
@@ -10357,7 +10342,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="206" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:17" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A206" s="15">
         <v>202</v>
       </c>
@@ -10396,7 +10381,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="207" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:17" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A207" s="15">
         <v>203</v>
       </c>
@@ -10691,7 +10676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A214" s="15">
         <v>210</v>
       </c>
@@ -12064,7 +12049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A253" s="15">
         <v>249</v>
       </c>
@@ -14902,6 +14887,18 @@
   </sheetData>
   <autoFilter ref="A4:Q270" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="23">
+    <mergeCell ref="B253:B258"/>
+    <mergeCell ref="B260:B270"/>
+    <mergeCell ref="B210:B211"/>
+    <mergeCell ref="B213:B215"/>
+    <mergeCell ref="B217:B245"/>
+    <mergeCell ref="B246:B250"/>
+    <mergeCell ref="B251:B252"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="B5:B40"/>
+    <mergeCell ref="B41:B72"/>
+    <mergeCell ref="B74:B86"/>
+    <mergeCell ref="B87:B90"/>
     <mergeCell ref="B164:B166"/>
     <mergeCell ref="B167:B181"/>
     <mergeCell ref="B182:B189"/>
@@ -14913,18 +14910,6 @@
     <mergeCell ref="B128:B136"/>
     <mergeCell ref="B137:B140"/>
     <mergeCell ref="B141:B163"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="B5:B40"/>
-    <mergeCell ref="B41:B72"/>
-    <mergeCell ref="B74:B86"/>
-    <mergeCell ref="B87:B90"/>
-    <mergeCell ref="B253:B258"/>
-    <mergeCell ref="B260:B270"/>
-    <mergeCell ref="B210:B211"/>
-    <mergeCell ref="B213:B215"/>
-    <mergeCell ref="B217:B245"/>
-    <mergeCell ref="B246:B250"/>
-    <mergeCell ref="B251:B252"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="L126" r:id="rId1" display="http://gpsnhatquang.com.vn:16840/" xr:uid="{AB90547F-F453-4F0C-B327-359B946F5497}"/>
@@ -14936,7 +14921,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" customWidth="1"/>
@@ -14951,34 +14936,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="52" t="s">
         <v>638</v>
       </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="54"/>
-      <c r="F1" s="54"/>
-      <c r="G1" s="54"/>
-      <c r="H1" s="54"/>
-      <c r="I1" s="55"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="53"/>
+      <c r="H1" s="53"/>
+      <c r="I1" s="54"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" s="56"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
-      <c r="D2" s="57"/>
-      <c r="E2" s="57"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="59"/>
+      <c r="A2" s="55"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="58"/>
     </row>
     <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="60" t="s">
+      <c r="A3" s="59" t="s">
         <v>67</v>
       </c>
-      <c r="B3" s="61"/>
+      <c r="B3" s="60"/>
       <c r="C3" s="10" t="s">
         <v>14</v>
       </c>
@@ -14991,15 +14976,15 @@
       <c r="F3" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="G3" s="66" t="s">
+      <c r="G3" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="67"/>
-      <c r="I3" s="67"/>
+      <c r="H3" s="66"/>
+      <c r="I3" s="66"/>
     </row>
     <row r="4" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="62"/>
-      <c r="B4" s="63"/>
+      <c r="A4" s="61"/>
+      <c r="B4" s="62"/>
       <c r="C4" s="11" t="s">
         <v>118</v>
       </c>
@@ -15014,18 +14999,18 @@
       <c r="F4" s="28" t="s">
         <v>637</v>
       </c>
-      <c r="G4" s="68" t="s">
+      <c r="G4" s="67" t="s">
         <v>18</v>
       </c>
-      <c r="H4" s="68"/>
+      <c r="H4" s="67"/>
       <c r="I4" s="8">
         <f>COUNTIF(Sheet1!Q:Q,"Tùng")</f>
         <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="62"/>
-      <c r="B5" s="63"/>
+      <c r="A5" s="61"/>
+      <c r="B5" s="62"/>
       <c r="C5" s="11" t="s">
         <v>98</v>
       </c>
@@ -15040,18 +15025,18 @@
       <c r="F5" s="28" t="s">
         <v>637</v>
       </c>
-      <c r="G5" s="69" t="s">
+      <c r="G5" s="67" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="68"/>
+      <c r="H5" s="67"/>
       <c r="I5" s="8">
         <f>COUNTIF(Sheet1!Q:Q,"Hậu")</f>
         <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="62"/>
-      <c r="B6" s="63"/>
+      <c r="A6" s="61"/>
+      <c r="B6" s="62"/>
       <c r="C6" s="11" t="s">
         <v>107</v>
       </c>
@@ -15063,21 +15048,21 @@
         <f>COUNTIFS(Sheet1!E:E,C6,Sheet1!D:D,"")</f>
         <v>13</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="F6" s="28" t="s">
         <v>637</v>
       </c>
       <c r="G6" s="50" t="s">
         <v>70</v>
       </c>
-      <c r="H6" s="51"/>
+      <c r="H6" s="50"/>
       <c r="I6" s="12">
         <f>COUNTIF(Sheet1!Q:Q,"Quang")</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="62"/>
-      <c r="B7" s="63"/>
+      <c r="A7" s="61"/>
+      <c r="B7" s="62"/>
       <c r="C7" s="11" t="s">
         <v>36</v>
       </c>
@@ -15095,8 +15080,8 @@
       <c r="I7" s="1"/>
     </row>
     <row r="8" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="62"/>
-      <c r="B8" s="63"/>
+      <c r="A8" s="61"/>
+      <c r="B8" s="62"/>
       <c r="C8" s="11" t="s">
         <v>231</v>
       </c>
@@ -15116,8 +15101,8 @@
       <c r="I8" s="1"/>
     </row>
     <row r="9" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="62"/>
-      <c r="B9" s="63"/>
+      <c r="A9" s="61"/>
+      <c r="B9" s="62"/>
       <c r="C9" s="11" t="s">
         <v>127</v>
       </c>
@@ -15137,8 +15122,8 @@
       <c r="I9" s="1"/>
     </row>
     <row r="10" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="62"/>
-      <c r="B10" s="63"/>
+      <c r="A10" s="61"/>
+      <c r="B10" s="62"/>
       <c r="C10" s="11" t="s">
         <v>279</v>
       </c>
@@ -15156,8 +15141,8 @@
       <c r="I10" s="1"/>
     </row>
     <row r="11" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="62"/>
-      <c r="B11" s="63"/>
+      <c r="A11" s="61"/>
+      <c r="B11" s="62"/>
       <c r="C11" s="11" t="s">
         <v>366</v>
       </c>
@@ -15175,8 +15160,8 @@
       <c r="I11" s="1"/>
     </row>
     <row r="12" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="62"/>
-      <c r="B12" s="63"/>
+      <c r="A12" s="61"/>
+      <c r="B12" s="62"/>
       <c r="C12" s="11" t="s">
         <v>35</v>
       </c>
@@ -15194,8 +15179,8 @@
       <c r="I12" s="1"/>
     </row>
     <row r="13" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="62"/>
-      <c r="B13" s="63"/>
+      <c r="A13" s="61"/>
+      <c r="B13" s="62"/>
       <c r="C13" s="11" t="s">
         <v>33</v>
       </c>
@@ -15213,8 +15198,8 @@
       <c r="I13" s="1"/>
     </row>
     <row r="14" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="62"/>
-      <c r="B14" s="63"/>
+      <c r="A14" s="61"/>
+      <c r="B14" s="62"/>
       <c r="C14" s="11" t="s">
         <v>8</v>
       </c>
@@ -15232,8 +15217,8 @@
       <c r="I14" s="1"/>
     </row>
     <row r="15" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="62"/>
-      <c r="B15" s="63"/>
+      <c r="A15" s="61"/>
+      <c r="B15" s="62"/>
       <c r="C15" s="11" t="s">
         <v>21</v>
       </c>
@@ -15251,8 +15236,8 @@
       <c r="I15" s="1"/>
     </row>
     <row r="16" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="62"/>
-      <c r="B16" s="63"/>
+      <c r="A16" s="61"/>
+      <c r="B16" s="62"/>
       <c r="C16" s="11" t="s">
         <v>20</v>
       </c>
@@ -15270,8 +15255,8 @@
       <c r="I16" s="1"/>
     </row>
     <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="62"/>
-      <c r="B17" s="63"/>
+      <c r="A17" s="61"/>
+      <c r="B17" s="62"/>
       <c r="C17" s="11" t="s">
         <v>4</v>
       </c>
@@ -15289,8 +15274,8 @@
       <c r="I17" s="1"/>
     </row>
     <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="62"/>
-      <c r="B18" s="63"/>
+      <c r="A18" s="61"/>
+      <c r="B18" s="62"/>
       <c r="C18" s="11" t="s">
         <v>68</v>
       </c>
@@ -15310,29 +15295,32 @@
       <c r="I18" s="1"/>
     </row>
     <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="62"/>
-      <c r="B19" s="63"/>
+      <c r="A19" s="61"/>
+      <c r="B19" s="62"/>
       <c r="C19" s="11" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="D19" s="8">
         <f>COUNTIFS(Sheet1!E:E,TongHopXLBH_2503!C19)</f>
-        <v>3</v>
-      </c>
-      <c r="E19" s="8"/>
+        <v>1</v>
+      </c>
+      <c r="E19" s="8">
+        <f>COUNTIFS(Sheet1!E:E,C19,Sheet1!D:D,"")</f>
+        <v>0</v>
+      </c>
       <c r="F19" s="21"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
     </row>
     <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="62"/>
-      <c r="B20" s="63"/>
+      <c r="A20" s="61"/>
+      <c r="B20" s="62"/>
       <c r="C20" s="11" t="s">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="D20" s="8">
-        <f>COUNTIFS(Sheet1!E:E,TongHopXLBH_2503!C20)</f>
+        <f>COUNTIFS(Sheet1!E:E,"*PK_*")</f>
         <v>1</v>
       </c>
       <c r="E20" s="8">
@@ -15345,79 +15333,63 @@
       <c r="I20" s="1"/>
     </row>
     <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="62"/>
-      <c r="B21" s="63"/>
-      <c r="C21" s="11" t="s">
-        <v>22</v>
+      <c r="A21" s="63"/>
+      <c r="B21" s="64"/>
+      <c r="C21" s="9" t="s">
+        <v>23</v>
       </c>
       <c r="D21" s="8">
-        <f>COUNTIFS(Sheet1!E:E,"*PK_*")</f>
-        <v>1</v>
+        <f>SUM(D4:D20)</f>
+        <v>266</v>
       </c>
       <c r="E21" s="8">
-        <f>COUNTIFS(Sheet1!E:E,C21,Sheet1!D:D,"")</f>
-        <v>0</v>
+        <f>SUM(E4:E20)</f>
+        <v>124</v>
       </c>
       <c r="F21" s="21"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
     </row>
-    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="64"/>
-      <c r="B22" s="65"/>
-      <c r="C22" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D22" s="8">
-        <f>SUM(D4:D21)</f>
-        <v>269</v>
-      </c>
-      <c r="E22" s="8">
-        <f>SUM(E4:E21)</f>
-        <v>124</v>
-      </c>
-      <c r="F22" s="21"/>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A22" s="1"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="51"/>
+      <c r="E23" s="51"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="52"/>
-      <c r="E24" s="52"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
+      <c r="G24" s="2"/>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="5"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
       <c r="G25" s="2"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="5"/>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="G26" s="2"/>
+      <c r="A26" s="7"/>
+      <c r="G26" s="3"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="7"/>
-      <c r="G27" s="3"/>
+      <c r="A27" s="4"/>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="4"/>
@@ -15451,16 +15423,13 @@
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="4"/>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="G6:H6"/>
-    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="D23:E23"/>
     <mergeCell ref="A1:I2"/>
-    <mergeCell ref="A3:B22"/>
+    <mergeCell ref="A3:B21"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="G5:H5"/>
